--- a/artfynd/A 44675-2023 artfynd.xlsx
+++ b/artfynd/A 44675-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44675-2023 artfynd.xlsx
+++ b/artfynd/A 44675-2023 artfynd.xlsx
@@ -675,60 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97480293</v>
+        <v>115618260</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Uppsala, Upl</t>
+          <t>Ströbykärret, SO om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629653.6819583362</v>
+        <v>629397</v>
       </c>
       <c r="R2" t="n">
-        <v>6644793.881468503</v>
+        <v>6644834</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +752,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-12-11</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-12-11</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,33 +781,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktor Eriksson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktor Eriksson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115617678</v>
+        <v>115618349</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,12 +830,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -846,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629641</v>
+        <v>629383</v>
       </c>
       <c r="R3" t="n">
-        <v>6644872</v>
+        <v>6644838</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +892,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>12 vinterståndare. Minst 75 bladrosetter. Växande på plant mossbelupet block i kanten av klibbal-grankärr. En meter från naturvårdssnitsel, alltså inom avverkningsanmälan. Hyggesröjt på margran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,65 +925,55 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115618349</v>
+        <v>97480293</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ströbykärret, SO om, Upl</t>
+          <t>Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629383</v>
+        <v>629653</v>
       </c>
       <c r="R4" t="n">
-        <v>6644838</v>
+        <v>6644793</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,27 +997,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2021-12-11</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2021-12-11</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>12 vinterståndare. Minst 75 bladrosetter. Växande på plant mossbelupet block i kanten av klibbal-grankärr. En meter från naturvårdssnitsel, alltså inom avverkningsanmälan. Hyggesröjt på margran.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,34 +1021,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Viktor Eriksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Viktor Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115617508</v>
+        <v>115617495</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1069,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1101,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629693</v>
+        <v>629698</v>
       </c>
       <c r="R5" t="n">
-        <v>6644799</v>
+        <v>6644785</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1136,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1146,7 +1131,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>12 bladrosetter. Inom avverkningsanmälan som hyggesröjts på margranar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,15 +1164,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115617856</v>
+        <v>115617508</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1194,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1226,10 +1211,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629594</v>
+        <v>629693</v>
       </c>
       <c r="R6" t="n">
-        <v>6644770</v>
+        <v>6644799</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,7 +1246,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1271,7 +1256,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1299,15 +1284,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115617842</v>
+        <v>115617526</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,8 +1312,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1343,10 +1331,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629596</v>
+        <v>629693</v>
       </c>
       <c r="R7" t="n">
-        <v>6644883</v>
+        <v>6644808</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1378,7 +1366,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1388,7 +1376,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>25 bladrosetter. Inom avverkningsanmälan som hyggesröjts på skiktet av margranar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,15 +1409,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115618260</v>
+        <v>115617538</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1439,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1468,10 +1456,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629397</v>
+        <v>629694</v>
       </c>
       <c r="R8" t="n">
-        <v>6644834</v>
+        <v>6644814</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1503,7 +1491,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1513,12 +1501,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>En vinterståndare.</t>
+          <t>Inom avverkningsanmälan som hyggesröjts på margranar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1546,15 +1534,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115618045</v>
+        <v>115617653</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1564,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1598,10 +1581,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629588</v>
+        <v>629662</v>
       </c>
       <c r="R9" t="n">
-        <v>6644710</v>
+        <v>6644893</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1633,7 +1616,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1643,12 +1626,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>4 bladrosetter. Nära naturvårdssnitsling.</t>
+          <t>Inom avverkningsanmälan som hyggesröjts på margranar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1676,15 +1659,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115617786</v>
+        <v>115617667</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629628</v>
+        <v>629656</v>
       </c>
       <c r="R10" t="n">
-        <v>6644883</v>
+        <v>6644888</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1763,7 +1741,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1773,7 +1751,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan som hyggesröjts på margranar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1801,15 +1784,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115618212</v>
+        <v>115617678</v>
       </c>
       <c r="B11" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,10 +1831,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629644</v>
+        <v>629641</v>
       </c>
       <c r="R11" t="n">
-        <v>6644737</v>
+        <v>6644872</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1888,7 +1866,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1898,7 +1876,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1926,15 +1904,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115617957</v>
+        <v>115617704</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1961,7 +1934,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1978,10 +1951,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>629571</v>
+        <v>629637</v>
       </c>
       <c r="R12" t="n">
-        <v>6644710</v>
+        <v>6644892</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2013,7 +1986,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2023,12 +1996,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>I avverkningsanmälans utkant, intill naturvårdssnitsling mot en gransumpskog.</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2056,15 +2024,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115617667</v>
+        <v>115617786</v>
       </c>
       <c r="B13" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2108,10 +2071,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>629656</v>
+        <v>629628</v>
       </c>
       <c r="R13" t="n">
-        <v>6644888</v>
+        <v>6644883</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2143,7 +2106,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2153,12 +2116,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan som hyggesröjts på margranar.</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2186,15 +2144,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115617653</v>
+        <v>115617795</v>
       </c>
       <c r="B14" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2174,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2238,10 +2191,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>629662</v>
+        <v>629623</v>
       </c>
       <c r="R14" t="n">
-        <v>6644893</v>
+        <v>6644888</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2273,7 +2226,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2283,12 +2236,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan som hyggesröjts på margranar.</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2316,15 +2264,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115618236</v>
+        <v>115617820</v>
       </c>
       <c r="B15" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2351,7 +2294,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2368,10 +2311,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>629648</v>
+        <v>629612</v>
       </c>
       <c r="R15" t="n">
-        <v>6644735</v>
+        <v>6644872</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2403,7 +2346,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2413,12 +2356,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>20 bladrosetter. En vinterståndare (dagens första).</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2446,15 +2384,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115617820</v>
+        <v>115617842</v>
       </c>
       <c r="B16" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2479,16 +2412,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2498,10 +2423,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>629612</v>
+        <v>629596</v>
       </c>
       <c r="R16" t="n">
-        <v>6644872</v>
+        <v>6644883</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2533,7 +2458,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2543,7 +2468,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2571,15 +2496,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115617538</v>
+        <v>115617856</v>
       </c>
       <c r="B17" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2606,7 +2526,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2623,10 +2543,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>629694</v>
+        <v>629594</v>
       </c>
       <c r="R17" t="n">
-        <v>6644814</v>
+        <v>6644770</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2658,7 +2578,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2668,12 +2588,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan som hyggesröjts på margranar.</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2701,15 +2616,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115617526</v>
+        <v>115617957</v>
       </c>
       <c r="B18" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2736,7 +2646,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2753,10 +2663,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629693</v>
+        <v>629571</v>
       </c>
       <c r="R18" t="n">
-        <v>6644808</v>
+        <v>6644710</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2788,7 +2698,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2798,12 +2708,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>25 bladrosetter. Inom avverkningsanmälan som hyggesröjts på skiktet av margranar.</t>
+          <t>I avverkningsanmälans utkant, intill naturvårdssnitsling mot en gransumpskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2831,15 +2741,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115617704</v>
+        <v>115618045</v>
       </c>
       <c r="B19" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2866,7 +2771,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2883,10 +2788,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629637</v>
+        <v>629588</v>
       </c>
       <c r="R19" t="n">
-        <v>6644892</v>
+        <v>6644710</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2918,7 +2823,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2928,7 +2833,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>4 bladrosetter. Nära naturvårdssnitsling.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2959,12 +2869,7 @@
         <v>115618195</v>
       </c>
       <c r="B20" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3086,15 +2991,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115617495</v>
+        <v>115618212</v>
       </c>
       <c r="B21" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3121,7 +3021,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3138,10 +3038,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629698</v>
+        <v>629644</v>
       </c>
       <c r="R21" t="n">
-        <v>6644785</v>
+        <v>6644737</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3173,7 +3073,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3183,12 +3083,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>12 bladrosetter. Inom avverkningsanmälan som hyggesröjts på margranar.</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3216,15 +3111,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115617795</v>
+        <v>115618236</v>
       </c>
       <c r="B22" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3251,7 +3141,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3268,10 +3158,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>629623</v>
+        <v>629648</v>
       </c>
       <c r="R22" t="n">
-        <v>6644888</v>
+        <v>6644735</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3303,7 +3193,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3313,7 +3203,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>20 bladrosetter. En vinterståndare (dagens första).</t>
         </is>
       </c>
       <c r="AD22" t="b">
